--- a/InputData/indst/_cement/CPCaOC/Cement Pathway Capital and Overhaul Costs.xlsx
+++ b/InputData/indst/_cement/CPCaOC/Cement Pathway Capital and Overhaul Costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CPCaOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A8F527-FD02-43FA-B3A3-878DA120595D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8E0243-1F86-4CDA-BBFB-B19180D70E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="140">
   <si>
     <t>CPCC Cement Pathway Capital Cost per Unit Annual Capacity</t>
   </si>
@@ -451,6 +451,15 @@
   </si>
   <si>
     <t>The ECRA range behind the dry kiln value varies a lot with plant size, so it is a rough cost for a typical new plant. No commercial plant exists for either the electric kiln or alternative chemistry, so both values are engineering or agency estimates of a mature plant. The kiln shell, tyre and drive costs in the overhaul build-up have almost no published per-ton data, and the ECRA component costs are European prices from 2009-2015. The overhaul-or-replace choice is not very sensitive to where the overhaul share falls within 10-25%, because building a new line at an existing site costs 50-105% of new-build cost (recent U.S. projects at Selma, Missouri; Ada, Oklahoma; and Laramie, Wyoming, from trade press). The cement module has no separate fixed operating and maintenance cost, so the overhaul cost covers the periodic capital reinvestment. The CRSW calibration weight depends on both costs and must be re-solved when either changes.</t>
+  </si>
+  <si>
+    <t>electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>The electric kiln with CCS is the electric kiln with a capture unit on its nearly pure CO2 stream, so it uses the electric kiln's value here (same kiln). Its capture is added through CCF (95 percent of calcination CO2 captured) and the CDSC capture inputs.</t>
   </si>
 </sst>
 </file>
@@ -523,7 +532,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -539,8 +548,14 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -845,21 +860,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="110.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.6328125" customWidth="1"/>
-    <col min="4" max="4" width="110.6328125" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="110.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="110.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -870,7 +885,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>31</v>
       </c>
@@ -878,7 +893,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>32</v>
       </c>
@@ -886,7 +901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2009</v>
       </c>
@@ -894,7 +909,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
@@ -902,7 +917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>33</v>
       </c>
@@ -910,7 +925,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>34</v>
       </c>
@@ -918,7 +933,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>35</v>
       </c>
@@ -926,7 +941,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>36</v>
       </c>
@@ -934,7 +949,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" s="7">
         <v>2010</v>
       </c>
@@ -942,7 +957,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
         <v>37</v>
       </c>
@@ -950,7 +965,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
         <v>38</v>
       </c>
@@ -958,7 +973,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
@@ -966,7 +981,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
         <v>40</v>
       </c>
@@ -974,7 +989,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
         <v>41</v>
       </c>
@@ -982,7 +997,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7">
         <v>2012</v>
       </c>
@@ -990,7 +1005,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
         <v>42</v>
       </c>
@@ -998,7 +1013,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
         <v>43</v>
       </c>
@@ -1006,7 +1021,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
         <v>76</v>
       </c>
@@ -1014,7 +1029,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
         <v>77</v>
       </c>
@@ -1022,7 +1037,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
         <v>78</v>
       </c>
@@ -1030,7 +1045,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7">
         <v>2018</v>
       </c>
@@ -1038,7 +1053,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="28" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>79</v>
       </c>
@@ -1046,7 +1061,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" ht="75" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
         <v>80</v>
       </c>
@@ -1054,7 +1069,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
         <v>81</v>
       </c>
@@ -1062,7 +1077,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
         <v>82</v>
       </c>
@@ -1070,7 +1085,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
         <v>83</v>
       </c>
@@ -1078,7 +1093,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7">
         <v>2023</v>
       </c>
@@ -1086,7 +1101,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
         <v>84</v>
       </c>
@@ -1094,7 +1109,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
         <v>85</v>
       </c>
@@ -1102,42 +1117,42 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B39" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B41" s="7">
         <v>2021</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="203" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>52</v>
       </c>
@@ -1145,7 +1160,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>53</v>
       </c>
@@ -1153,7 +1168,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>86</v>
       </c>
@@ -1161,7 +1176,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>87</v>
       </c>
@@ -1169,7 +1184,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>134</v>
       </c>
@@ -1177,12 +1192,20 @@
         <v>135</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1204,19 +1227,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1224,7 +1247,7 @@
         <v>3500000000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1232,12 +1255,12 @@
         <v>3750000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1245,7 +1268,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1253,7 +1276,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1264,7 +1287,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1272,7 +1295,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -1280,12 +1303,12 @@
         <v>1.0860000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1293,7 +1316,7 @@
         <v>378000000</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1301,7 +1324,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1309,7 +1332,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1317,12 +1340,12 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>58</v>
       </c>
@@ -1330,7 +1353,7 @@
         <v>204.4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>59</v>
       </c>
@@ -1338,7 +1361,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -1346,7 +1369,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -1354,7 +1377,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1362,7 +1385,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -1370,7 +1393,7 @@
         <v>1.181</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1401,7 @@
         <v>251.107</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1386,12 +1409,12 @@
         <v>229.59399999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -1399,7 +1422,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -1407,7 +1430,7 @@
         <v>500000000</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -1415,7 +1438,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>69</v>
       </c>
@@ -1431,18 +1454,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1451,7 +1474,7 @@
         <v>933.33333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1460,12 +1483,12 @@
         <v>255.21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>106</v>
       </c>
@@ -1474,7 +1497,7 @@
         <v>255.21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -1483,12 +1506,12 @@
         <v>255.21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1497,7 +1520,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1506,12 +1529,12 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>71</v>
       </c>
@@ -1520,7 +1543,7 @@
         <v>299.20749291839735</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -1529,7 +1552,7 @@
         <v>249.43856098794541</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -1538,12 +1561,12 @@
         <v>299.20749291839735</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1552,7 +1575,7 @@
         <v>502.3356153443911</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -1561,7 +1584,7 @@
         <v>251.16780767219555</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>109</v>
       </c>
@@ -1578,18 +1601,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA01D23-0151-4CB2-91AE-B01E33E3465D}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60.6328125" customWidth="1"/>
-    <col min="2" max="3" width="22.6328125" customWidth="1"/>
+    <col min="1" max="1" width="60.5703125" customWidth="1"/>
+    <col min="2" max="3" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>90</v>
       </c>
@@ -1600,7 +1623,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1613,7 +1636,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1626,7 +1649,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1639,12 +1662,12 @@
         <v>41.913200391178655</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
       <c r="B7">
-        <f>'CPCaOC-new'!B5</f>
+        <f>'CPCaOC-new'!B6</f>
         <v>502.3356153443911</v>
       </c>
       <c r="C7">
@@ -1652,7 +1675,7 @@
         <v>70.367533594145911</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -1661,12 +1684,12 @@
         <v>0.14008071784021001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -1674,7 +1697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>95</v>
       </c>
@@ -1682,7 +1705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -1690,7 +1713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>97</v>
       </c>
@@ -1698,7 +1721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>98</v>
       </c>
@@ -1706,7 +1729,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1714,7 +1737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1723,7 +1746,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>101</v>
       </c>
@@ -1732,7 +1755,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -1751,10 +1774,10 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -1762,7 +1785,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1771,7 +1794,7 @@
         <v>255.21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1780,7 +1803,7 @@
         <v>255.21</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1789,11 +1812,20 @@
         <v>299.20749291839735</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>299.20749291839735</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <f>Calc!B21</f>
         <v>502.3356153443911</v>
       </c>
@@ -1808,10 +1840,10 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -1819,7 +1851,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1828,7 +1860,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1837,7 +1869,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1846,11 +1878,20 @@
         <v>41.913200391178655</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>41.913200391178655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <f>Overhaul!C7</f>
         <v>70.367533594145911</v>
       </c>
